--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -8,13 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_표지" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_SEC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Yahoo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Nasdaq" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Damodaran" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SPDR" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_동종서비스" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_SEC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Yahoo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Nasdaq" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Damodaran" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_SPDR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_라운드별발견이력" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_R1_기관중심" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_R2_데이터중심" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_R3_동종서비스역추적" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_R4_규제구조기록" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_카테고리별" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_슬롯매핑" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_즉시이득" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_동종서비스조합패턴" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,19 +41,19 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00CC0000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00CC0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,10 +83,10 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -450,16 +457,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>데이터 소스 카탈로그 ① — 이미 쓰는 5개 기관 (STEP 997)</t>
+          <t>데이터 소스 카탈로그 ①+② (STEP 997·998)</t>
         </is>
       </c>
     </row>
@@ -480,14 +487,2156 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>범위: SEC · Yahoo Finance · Nasdaq Trader · Damodaran(NYU) · SPDR/State Street</t>
+          <t>① STEP997: 이미 쓰는 5개 기관(SEC·Yahoo·Nasdaq·Damodaran·SPDR)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>탭 순서: 요약 → SEC → Yahoo → Nasdaq → Damodaran → SPDR → 동종서비스</t>
+          <t>② STEP998: 3라운드 전수 조사(R1 기관중심 27 · R2 데이터중심 29 · R3 동종서비스역추적 28 · R4 규제기록 3) = 누적 92개 소스</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>수렴 판정: R4/R1 = 11.1%(10%규칙 형식상 초과하나 R4 3건 전부 슬롯 무관 + R2·R3 대비 급감 → 종결, 장은태 판정 대기)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>R3 — 동종서비스 역추적(28개 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>신규 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>동종서비스 자체 공개 소스</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Market Intelligence·Fiscal AI·Nasdaq UTP·Hiive·TipRanks·Quartr·BlueMatrix·ICE Market Data·QuoteMedia(CSI)·True FX·Trading Economics·Koyfin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>비교글 발견</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Calcbench·Daloopa·FinancialData.Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>OSS 의존목록 발견(OpenBB·pandas-datareader)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EconDB·Ken French Data Library·Bank of Canada·World Bank·Eurostat·OECD·Benzinga·Biztoc·Deribit·TMX Group·Tradier·Seeking Alpha</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>R4 — 규제/구조 기록(3개 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>무엇</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>슬롯 매핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SEC Form 13F 데이터셋</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>분기별 기관투자자 보유내역 전체 벌크(무료)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>16슬롯 밖(소유구조 데이터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SEC 내부자거래 데이터셋(Form3/4/5 벌크)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>분기별 내부자거래 전체 벌크(무료)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>16슬롯 밖(소유구조 데이터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>델라웨어주 법인등기소</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>법인 존재확인(무료) / 상태(active·dissolved, $10~20 유료)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>상장상태/폐지위험 — 핵심 필드가 유료라 실사용 어려움</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>카테고리 분류(33개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>대표 소스</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>핵심 정의</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>시가총액·기말발행주식수 기준</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(우리 정본, SEC 주식수×종가로 직접 조립)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>975 정본 — 외부 대조 시 이 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>시가총액·가중평균희석주식수 기준</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>일부 벤더(구체 미확인)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>975에서 8.29% 차이 확인 — 다른 카테고리</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>시가총액·계산기준 미명시(벤더 사전계산)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo(quote/quoteSummary)·Nasdaq스크리너/quote·FMP·Alpha Vantage·EODHD·Wisesheets 등</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>위 1·2 중 어느 쪽인지 불명 — 검증 없이 신뢰 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>발행주식수·SEC원문 태그(시점 명시)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SEC dei:EntityCommonStockSharesOutstanding</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>우리 정본</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>발행주식수·이력 시계열(free)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SEC DERA 벌크(FSDS)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>유일한 free 다년 시계열</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>발행주식수·벤더 스냅샷(시점 불명)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo defaultKeyStatistics·Alpha Vantage OVERVIEW·Finviz 등</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>현재값만, 이력 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>주가·비조정 종가</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>각 거래소·벤더</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>주가·배당/분할조정 종가</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>stooq·Tiingo·EODHD·Yahoo chart 등</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>조정방식 대부분 미명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>재무제표·SEC원문 태그(추적가능)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts/벌크ZIP/FSDS·edgartools·xbrl.us·오픈소스 XBRL파서군</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>우리 정본 — 태그명 보존</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>재무제표·벤더 정규화(추적불가)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>FMP·Alpha Vantage·Tiingo·EODHD·SimFin·WSJ 등 대다수</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>재분류 규칙 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>재무제표·벤더 정규화+출처표기(부분추적)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Polygon(include_sources)·Wisesheets(XBRL인용)·Intrinio(as-reported)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>정규화하되 원문 링크 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류·GICS(라이선스, 무료경로 없음)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>MSCI/S&amp;P DJI GICS Direct</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>무료 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류·GICS 근사(ETF보유 역산, S&amp;P500 한정)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SPDR 11섹터 ETF(정본)·Morningstar연계ETF(대체재, 커버리지 동급)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>~500~530종목 상한</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류·비GICS 자체체계(서로 대체 불가)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>나스닥(12개)·야후(11개,GICS 1:1대응)·SEC SIC·Damodaran(94개)·ICB(FTSE, 45섹터)·Morningstar(11개)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>체계가 달라 섞으면 안 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>업종 집계배수·연1회 학술</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran(pedata·pbvdata·psdata·vebitda 등)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>우리 정본</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>업종 집계배수·반기 이상(부분무료)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Siblis Research(반기)·Yardeni(주간, 차트뿐)·stockanalysis.com(주기미상)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>문서화된 방법론은 Siblis뿐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>업종 베타·연1회 학술(대체 소스 없음 확인)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran betas.xls</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>R1~R4 전체에서 무료 대체재 못 찾음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>ERP·연1회 시장내재</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran(histimpl.xls 포함)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>시장가격 역산</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>ERP·분기 서베이(다른 정의)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Duke CFO Survey(Graham&amp;Harvey)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>실무자 기대치, 시장내재와 다른 개념 — 대체재 아니라 병기용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>무위험수익률·매일 국채수익률</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>FRED DGS10·Treasury.gov 원천</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>같은 CMT곡선, 상호 대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>무위험수익률·연1회 학술 스칼라</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran wacc.xls 상단값</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>현재 정본, 갱신빈도 낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>법인세율·연방 고정</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IRS(21%, 2018~)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>입법 전까지 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>법인세율·주별</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Tax Foundation(연1회, 입법과 동주기)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran countrytaxrates와 별도 층위</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>법인세율·업종별 실효세율</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran taxrate.xls</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>현재 정본</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>신용스프레드·매일 등급별</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>FRED ICE BofA OAS(IG AAA~BBB, HY BB~CCC)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>R2 최대 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>신용스프레드·연1회 학술(등급→스프레드 룩업)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran ratings.xls</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>현재 정본, 종목별 부채비용 산출 가능(997 발견)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>배당·이벤트 캘린더</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>나스닥 dividends calendar(현재 사용)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>배당·개별종목 이력</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Tiingo·EODHD·FMP·Polygon 등 다수</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>상용 API 대부분 보유</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>상장상태/폐지위험·거래소 자체신고(공식정의)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>나스닥 Financial Status 플래그(997 발견, 미사용)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>D/E/Q 코드 공식 정의 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>상장상태/폐지위험·SEC 공식(구조화 검색)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>SEC Form 25(거래소 상장폐지)·Form 15(등록말소, R4 발견)</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>서로 다른 시점 신호(15가 더 이를 수 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터·SEC 공식(CIK 중심)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>company_tickers_exchange.json(현재 정본)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터·거래소 심볼 디렉터리</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>나스닥 심볼디렉터리(현재 정본)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터·글로벌 식별자 매핑(CIK 없음)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>OpenFIGI(티커/CUSIP/ISIN↔FIGI)·GLEIF(ISIN↔LEI)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>CIK 브릿지는 티커 조인 필요(미검증)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>슬롯 매핑(20개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>슬롯</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>지금 쓰는 소스(우선순위)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>자격있는 후보(카테고리#)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>요구정밀도</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>검증방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>시가총액</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo 배치조회(정본, us_market_cap)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>카테고리3 전부(Nasdaq스크리너 등) — 전부 계산기준 미명시라 검증 없이 못 씀</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답(Q1 분모)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>카테고리1(기말발행×종가)과 대조해야 신뢰 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>발행주식수</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SEC XBRL 태그(역DCF), Yahoo 부수값(밸류)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>카테고리4(SEC 정본)·5(이력, 미사용)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>카테고리4와 직접 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>주가</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>us_stock_perf(야후계열, 표시용)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>카테고리7·8 다수</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답(역DCF sharePrice)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>거래소 종가와 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts(정본)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9(edgartools 등, 같은 원문)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>이미 원문 — 검증 불요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>자기자본(보통주)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts(963 정책)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts(폴백 포함)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts(969 3분류)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>비영업자산/현금</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>SEC companyfacts</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>카테고리9</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>원문</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran countrytaxrates(한계세율, US행)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>카테고리22(IRS 연방)·23(주별)·24(업종실효)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>순위만 필요할 수 있음(WACC 구성요소)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>IRS 21%와 국가한계세율 정합 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>자본지출률</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>원전 T5 방식(내부 계산)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>후보 1개뿐(원전 계산 방식 자체가 유일 정의, 외부 소스 대체 불가)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>원전 대조표</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>운전자본률</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>원전 T4 방식(내부 계산)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>후보 1개뿐(동일 사유)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>원전 대조표</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>무위험수익률</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran wacc.xls 상단값(연1회)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>카테고리20(FRED/Treasury 매일) —  갱신빈도 개선 후보</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답(WACC)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FRED DGS10과 직접 대조(당일 대조 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran wacc.xls 상단값(연1회)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>카테고리19(Duke서베이, 분기·다른정의)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답(WACC)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Duke서베이와 정의 차이 공개 후 병기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>베타</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran betas.xls(업종, 연1회)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>후보 1개뿐(R1~R4 전체에서 무료 대체 못 찾음)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답이나 업종 대표값이라 개별종목은 근사</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>대체 소스 없어 검증 불가(원전 신뢰 외 방법 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>신용스프레드</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran ratings.xls/wacc.xls(연1회)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>카테고리25(FRED ICE BofA OAS, 매일) —  최대 발견, 갱신빈도 개선 후보</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>값 자체가 답(부채비용)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>FRED와 등급별 직접 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>resolveSector() 0~4순위(SPDR→Damodaran→형제→야후→미분류)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>카테고리14(비GICS 다수) 전부 이미 후보에 포함됨</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>순위/그룹핑만 필요(업종 대비용)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>기존 3중 대조 체계 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>업종배수</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran pedata/pbvdata/psdata/vebitda(연1회)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>카테고리16(Siblis 등, 반기)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>순위/비교만 필요(업종 대비 분자)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Siblis와 방향성 대조 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>업종베타</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran betas.xls</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>후보 1개뿐(=16과 동일 소스, 슬롯만 다름)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>순위만 필요(WACC 구성요소 산출용)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>검증 불가(원전 신뢰)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>즉시 이득 통합 목록(997+998, 12건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>발견</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>어느 슬롯</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>예상 이득</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>선결 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1(997)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo/Nasdaq 시총 대체경로</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>#1 시가총액</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>미해결14번(LOCAL_OK_PROD_FAIL) 우회 가능성</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>계산기준 검증(카테고리1·2·3 구분) 먼저</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2(997)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran ratings.xls(종목별 부채비용)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>#17 신용스프레드</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>업종평균 대신 종목별 이자보상배율 기반 부채비용</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>원전대조표</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>3(997)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran fundgrEB.xls(EBIT 성장률)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>역DCF 성장경로(층5, 범위 밖 슬롯)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>"가장 큰 구멍"의 비컨센서스 대안</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>원전대조표</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>4(997)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran histimpl.xls(내재ERP)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>#15 ERP</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>원전대조표, 카테고리18 내부 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>5(997)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>나스닥 Financial Status 플래그</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>상장상태/폐지위험(범위 밖 슬롯)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>상폐위험 조기신호</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>코드 없음, 데이터 이미 우리 유니버스 갱신 스크립트가 지나감</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>6(997)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>SPDR 전 상품군(섹터ETF 외)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>#18 섹터분류</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>산업(서브섹터) 근사 가능성</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>라이선스 문구 법무검토(997에서 이미 등재)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7(998,R2)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>FRED ICE BofA OAS(등급별 매일 신용스프레드)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>#17 신용스프레드</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran 연1회→매일 갱신으로 정밀도 개선 가능</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>카테고리25↔26 정의 일치 확인(다른 방법론일 수 있음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>8(998,R2)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FRED/Treasury 매일 국채수익률</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>#14 무위험수익률</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Damodaran 연1회→매일</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>카테고리20↔21 정의 일치 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9(998,R2)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Duke CFO Survey(분기 ERP)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>#15 ERP</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>서베이 기반 병기용(대체 아님)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>정의 차이(서베이 vs 시장내재) 화면 공개 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>10(998,R2)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>edgartools(OSS, SEC 원문 그대로 재접근)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>#4~#10 재무제표 전체</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>코드 대안(현재 route.ts 자체 파서 유지 이유 재확인용)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>이득이 아니라 "현재 방식이 최선"이라는 대조 자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>11(998,R2)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>OpenFIGI(무료 식별자 매핑)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>#33(종목마스터, 슬롯 밖)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CIK-티커 매핑 교차검증</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>CIK 필드 없음 — 티커 조인 검증 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>12(998,R3)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Market Intelligence가 동종서비스 대다수의 실제 소스</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>(참고, 슬롯 없음)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>우리 "SEC원문+Damodaran" 조합이 여전히 드문 조합임을 재확인</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>판단 대상 아님(정보)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>동종 US 서비스 조합 패턴(997)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>서비스</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>SEC 원문 직접 사용?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Damodaran 사용?</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>어떻게 조합하는가</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>(S&amp;P Global Market Intelligence가 정규화한 것을 씀)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>펀더멘털=S&amp;P Global, 가격=ICE — 원문 XBRL 미접촉</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>stockanalysis.com</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>(S&amp;P Global·Fiscal AI 이원화)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>데이터 종류별로 벤더를 따로 명시(펀더멘털·가격·애널리스트·기업행동·ETF보유 전부 별도 벤더) — "카테고리별 벤더 분리"가 이들의 패턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Finbox</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>(S&amp;P Global 정규화)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>유일하게 확인된 SEC+Damodaran 병존 사례</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>단, 같은 화면에 병치할 뿐 하나의 계산 파이프라인으로 융합하지 않음(Damodaran 자본비용 테이블을 별도 탭/섹션으로 노출)</t>
         </is>
       </c>
     </row>
@@ -497,166 +2646,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>기관별 엔드포인트 개수 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>기관</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>전수 확인된 엔드포인트/데이터셋 수</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>우리가 쓰는 수</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SEC (EDGAR)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>5(companyfacts·companyconcept·submissions·bulk zip·company_tickers_exchange)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>frames는 조회는 하나 개별판정엔 안 씀(횡단검증 전용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance(비공식)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>25+ 모듈/엔드포인트</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>4(quote·quoteSummary[assetProfile]·chart·fundamentalsTimeSeries)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>quoteSummary 자체는 30여 서브모듈 중 1개만 씀</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Nasdaq Trader/api.nasdaq.com</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>4(symdir 2개·screener·ipo/dividends calendar)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>대부분 비공식(api.nasdaq.com), symdir 2개만 공식 문서 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Damodaran(NYU)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>약 30개 파일(미국 컷 기준, 지역변형 제외)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>8(indname·taxrate·countrytaxrates·wacc·betas·capex·wcdata + totalbeta는 미사용)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>ratings.xls·fundgrEB.xls·histimpl.xls가 즉시 검토 후보(아래 §신규 발견 참조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>SPDR/State Street</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>5개 제품군(섹터ETF·핵심지수ETF·산업ETF·팩터ETF·펀드메타파일)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>1(11개 섹터 ETF 홀딩스)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>spdr-product-data-us-en.xlsx 마스터 파일 신규 발견(전 SPDR 펀드 메타데이터 1파일)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1347,7 +3336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2414,7 +4403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3580,7 +5569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4162,7 +6151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4524,25 +6513,193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>라운드별 신규 발견 수 · 수렴 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>라운드</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>각도</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>조사 대상</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>신규 발견</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>R1 대비 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>기관 중심("누가 주는가")</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>27개 기관(공공6·거래소4·분류4·상용API9·기관급4)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>27(기준)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>데이터 중심 역방향("이 값을 어디서 받나", 16개 값별 검색)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>107.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>타자 역추적("동종서비스는 뭘 쓰나" + 비교글 + OSS 의존목록)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>103.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>규제/구조 기록 중심("규제 때문에 존재하는 데이터")</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>13F·내부자거래·CAT·DTCC·주정부 등기소·Form15 등 8건</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>동종 US 서비스 조합 패턴</t>
+          <t>R1 — 기관 중심 조사(27개)</t>
         </is>
       </c>
     </row>
@@ -4550,80 +6707,964 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>기관</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SEC 원문 직접 사용?</t>
+          <t>핵심 데이터셋</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Damodaran 사용?</t>
+          <t>정의</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>어떻게 조합하는가</t>
+          <t>형식</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>갱신</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>슬롯</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Simply Wall St</t>
+          <t>FRED</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>(S&amp;P Global Market Intelligence가 정규화한 것을 씀)</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
+          <t>DGS3MO/DGS2/DGS10/DGS30(국채수익률) · BAMLC0A1CAAA~BBB(IG 등급별 스프레드) · BAMLH0A1HYBB~HYC(HY 등급별) · BAA10Y(Baa-10Y스프레드)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>재무부 CMT 곡선 재발행("Market Yield... at N Constant Maturity") · ICE BofA OAS(시총가중 등급별 지수)</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>펀더멘털=S&amp;P Global, 가격=ICE — 원문 XBRL 미접촉</t>
+          <t>JSON/CSV/XML</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>무료키 필요</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>무위험수익률·신용스프레드</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>stockanalysis.com</t>
+          <t>US Treasury(fiscaldata·home.treasury.gov)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>(S&amp;P Global·Fiscal AI 이원화)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+          <t>Daily Par Yield Curve Rates(1개월~30년)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>CMT 원천(FRED가 재발행하는 바로 그 곡선), NY Fed 오후3:30 지표호가 기반</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>데이터 종류별로 벤더를 따로 명시(펀더멘털·가격·애널리스트·기업행동·ETF보유 전부 별도 벤더) — "카테고리별 벤더 분리"가 이들의 패턴</t>
+          <t>CSV/XML</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>무위험수익률(원천)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Finbox</t>
+          <t>BLS</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>(S&amp;P Global 정규화)</t>
+          <t>CPI·PPI·고용 시계열(Public API v2)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>유일하게 확인된 SEC+Damodaran 병존 사례</t>
+          <t>조사 기반 공식 통계</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>단, 같은 화면에 병치할 뿐 하나의 계산 파이프라인으로 융합하지 않음(Damodaran 자본비용 테이블을 별도 탭/섹션으로 노출)</t>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>무료키(없어도 25콜/일)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>월별</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>해당없음(거시, 16슬롯 밖)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>BEA</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>NIPA Table 1.14(법인세전이익·법인세·세후이익, 국민계정 집계)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>거시 집계, 기업단위 아님</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>JSON/XML</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>무료키</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>법인세율(약한 대리, 집계치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>FINRA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Reg SHO 일별 공매도량 · 공매도잔고(월2회) · Threshold List(상환실패 지속종목)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>미명시 세부</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Flat file/CSV</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>대부분 불필요</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>일/월2회</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>무료(비상업 조건)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>상장상태/폐지위험(약한 대리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CFTC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Commitments of Traders(COT, 선물 포지션)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>상품선물 롱숏 포지션(국채·주가지수선물 포함)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>JSON/CSV/XML(Socrata)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>불필요(토큰 선택)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>주별(금)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>해당없음(선물시장 구조, 16슬롯 밖)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>핵심 데이터셋</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>무료 여부</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>슬롯</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Security Master·TAQ 이력·실시간 피드</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>문서화됨(스펙PDF)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>전부 유료/기업계약</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터·주가(전부 유료라 실사용 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cboe</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>옵션 레퍼런스데이터(무료 CSV) · DataShop(유료, 14일 체험)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>미명시</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>옵션 종목목록만 무료</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터(옵션 한정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>OTC Markets</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Security Master·실시간시세·OTC Disclosure API</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>미명시(문서 접근 실패, 미검증)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>전부 유료로 보임(무료API 확인 안 됨)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>종목마스터·상장상태(현재 나스닥 파생 데이터보다 권위 있으나 접근 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>IEX(거래소)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>HIST(과거 틱데이터) 무료 · TOPS/DEEP(실시간)은 계약 필요</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>IEX Cloud(무료 개발자API)는 2024-08-31 종료 확정 — 후속업체는 IEX와 무관</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>과거 틱데이터만 무료</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>주가(과거 틱, 일상 파이프라인엔 안 맞음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>체계(무료)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>종목별 매핑(유료여부)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>슬롯</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>MSCI(GICS 공동소유)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>방법론 PDF 무료</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>GICS Direct 라이선스</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류(체계 참고만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>S&amp;P DJI(GICS 공동소유)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>지수 방법론 PDF 무료</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>라이선스, 무료 구성종목 목록도 공식으로는 없음(위키·Barchart 등 비공식 미러만 존재)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류(체계 참고만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>FTSE Russell</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>ICB 구조 정의 XLSX 무료(11산업/20슈퍼섹터/45섹터/173서브섹터)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>종목별 라이선스 필요</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류(다른 체계, 대체재 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>개별종목 페이지 무료(대량조회 ToS 위반)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Morningstar연계 ETF로 근사 가능하나 SPDR과 커버리지 동급</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류(SPDR과 대체 관계, 확장 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>무료tier(정확한 한도)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>재무데이터 원문추적성</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>슬롯</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Polygon.io/Massive</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>5콜/분, EOD만, 2년치</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>include_sources=true로 부분 추적(정규화+출처표기)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>전체(유료전환 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Financial Modeling Prep</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>250콜/일</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>미확인(공식문서 접근 실패)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Alpha Vantage</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>25콜/일</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>"GAAP/IFRS로 정규화" 자인</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Tiingo</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>1,000콜/일(가격), 재무는 Dow30 한정</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>미공개 서드파티</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>가격 위주</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Intrinio</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>사실상 없음(2주 체험뿐)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>as-reported 엔드포인트=원문+출처링크(가장 추적성 좋음)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>전체(비쌈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>EODHD</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>20콜/일</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>미명시, GICS 4단계 필드 명시 보유(9곳 중 유일)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류(GICS 필드 있음, 출처 신뢰도 별도 확인 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Twelve Data</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>8콜/분·800/일, 완전재무는 $329/월</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Finnhub</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>60콜/분이나 비상업용 한정</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>financials-reported=원문 태그명+출처filing 보존(사실상 SEC 재서빙)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>전체(단 상업이용 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Nasdaq Data Link(구Quandl)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>무료 WIKI는 2018-03 영구중단</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar=정규화, 유료</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>사실상 무료 대안 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>고유 카테고리</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>LSEG/Refinitiv</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>I/B/E/S 컨센서스 추정치(방법론 공개: SmartEstimate=이상치 제외+최신성 가중+애널리스트 트랙레코드)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>~$1,500-3,000/월 플랫폼 + 데이터 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>BEst 컨센서스(방법론 비공개)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>~$24,000-30,000/년/좌석</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>FactSet</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Revere 택소노미(7,000+ 세분류, GICS보다 깊음)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>계약별(비공개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>S&amp;P Capital IQ</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Visible Alpha(200+ 브로커·100만+ 컨센서스 라인아이템, 포함기준 문서화)</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>$12,000~$300,000+/계약</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>R2 — 데이터 중심 역방향 검색(29개 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>신규 발견</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>핵심 한줄</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>시가총액/주가/배당</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>stooq.com·Marketstack·Finviz·macrotrends.net·Wisesheets·Financial Datasets·Eulerpool·DTCC·Databento·sec-api.io</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>발행주식수의 free 이력 시계열은 SEC DERA 벌크(우리가 이미 씀)가 사실상 최선 — 대부분 스냅샷 1건뿐</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>순이익/자기자본/매출/부채</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>xbrl.us·edgartools(OSS)·OpenBB·SimFin·WSJ(FactSet소싱)·Simply Wall St·stockanalysis.com·오픈소스 XBRL 파서군</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>edgartools(OSS, MIT)가 get_raw_data()로 SEC 원문 그대로 접근 — 우리 원칙과 완전히 부합(단, SEC를 대체가 아니라 같은 소스에 접근하는 다른 클라이언트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>업종배수/베타/ERP/세율/신용스프레드</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Siblis Research·Yardeni Research·FullRatio·GuruFocus·CSIMarket·Fernandez(IESE 서베이)·Duke CFO Survey(Graham&amp;Harvey)·Tax Foundation·IRS</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Duke CFO Survey = 분기 갱신 ERP(Damodaran 연1회보다 빠름, 단 서베이 정의라 시장내재치와 다른 개념) ·  FRED ICE BofA OAS = 매일 등급별 신용스프레드(위 R1a에 이미 기재, 가장 강한 발견)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>섹터분류/상장폐지위험/종목마스터</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>OpenFIGI·GLEIF</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>OpenFIGI(Bloomberg 무료 공개, 티커/CUSIP/ISIN↔FIGI 매핑, CIK 필드는 없음) · GLEIF(LEI, 무료 ISIN-LEI 매핑)</t>
         </is>
       </c>
     </row>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Damodaran(histimpl.xls 포함)</t>
+          <t>🔴 **정정(1002) — `histimpl.xls`(연간)와 `ERPbymonth.xlsx`(월간, 1001 발견)는 서로 다른 파일이다.** Damodaran</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>시장가격 역산</t>
+          <t>시장가격 역산. 우리가 실제로 쓰는 값(wacc.xls 상단)은 `ERPbymonth.xlsx`의 페어드 계열과 일치</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>무위험수익률·매일 국채수익률</t>
+          <t>무위험수익률·매일 국채수익률(raw Treasury)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>같은 CMT곡선, 상호 대체 가능. 🔴 **STEP999 대조 완료**: Damodaran 정의("10-year Treasury bond rate", 원문 확인)와 **완전 일치** — 정의 층위에서 교체가 원전 이탈이 아님을 확인. 2026-01-05 값 3.95% vs 2026-08-07 FRED 4.65% = **70bp 차이**, 1년 변동폭 78bp(2025-10-22 3.97%~2026-07-31 4.75%). 20종목 표본 재계산 결과 65%(13/20) verdict 표현 변화·5%(1/20) 카테고리 자체 전환(CDNS: years→over_cap) — `docs/probe_999_fred_damodaran.json`</t>
+          <t>🔴 **정정(1002) — STEP999의 "완전 일치" 판정은 값 층위에서 오류였다.** 999는 정의 문구("10-year Treasury bond rate")만 대조해 일치를 확인했으나, **Damodaran이 실제로 ERP와 짝지어 쓰는 값은 raw Treasury가 아니라 별도의 자체조정 "$ Riskfree Rate" 계열**임을 1001이 발견했다(`ERPbymonth.xlsx` 직접 개봉, 산식 미공개). 우리 저장값 3.95%는 raw Treasury(FRED·`T.Bond Rate`≈4.18%)가 아니라 "$ Riskfree Rate"(0.0395)와 정확 일치 — **정의는 같은 말을 써도 실제 계열이 다르다.** 🔴 **결론: 카테고리20(raw Treasury, FRED 포함)은 #14 슬롯의 후보 부적격.** 유일한 유효 후보는 `ERPbymonth.xlsx`의 "$ Riskfree Rate"(카테고리18 내부, 짝인 ERP와 함께) — `docs/probe_999_fred_damodaran.json`(원 판정, 정정 대상)·`docs/probe_1001_erp_pair.json`(정정 근거)</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>현재 정본, 갱신빈도 낮음. 🔴 **STEP999 부수발견**: as_of(2026-01-05) 당일 실제 DGS10은 4.15~4.19%대였는데 저장값은 3.95% — 그 시점에도 이미 ~20bp 괴리가 있었다(원인 미상, 판정 필요)</t>
+          <t>현재 정본이나 🔴 **실질 정체(1001) — 2026-01-05 이후 7개월+ 미갱신**(HTTP Last-Modified 실측), "연1회"라는 서술과 달리 사실상 갱신이 멈춰 있다. 🔴 **STEP999 부수발견의 정체 해소(1001)**: as_of(2026-01-05) 당일 실제 raw DGS10은 4.15~4.19%대였는데 저장값은 3.95% — 그 괴리는 "원인 미상"이 아니라 **Damodaran의 "$ Riskfree Rate" 계열이 raw Treasury와 원래 다른 숫자이기 때문**이었다(1001에서 완전 해소, 판정 불필요 상태로 전환)</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Damodaran wacc.xls 상단값(연1회, 사실상 정체 7개월+)</t>
+          <t>Damodaran wacc.xls 상단값(연1회라 서술되나 실질 정체 7개월+)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>🔴 **단, #15(ERP)와 함께 바꿔야 함(의존관계①·ⓐ짝제약) — 단독 교체 금지, 1001에서 실제로 이 실수를 함.** 카테고리20(FRED/Treasury 매일)은 rf만 줄 뿐이라 **단독으로는 후보가 못 됨**. 유효 후보 = 카테고리18 내부의 `ERPbymonth.xlsx`(rf·ERP 짝 제공, 1001 발견)</t>
+          <t>🔴 **카테고리20(FRED/Treasury raw) = 부적격, 정정(1002).** 짝 제약(의존관계①·ⓐ) 때문만이 아니다 — **raw Treasury 자체가 Damodaran이 실제로 쓰는 "$ Riskfree Rate" 계열과 다른 숫자**임을 1001이 확인했다(999의 "완전 일치"는 정의 문구만 대조한 오판, 카테고리20 참조). 짝을 맞춰 FRED를 쓰더라도 짝지을 ERP 자체가 "$ Riskfree Rate" 기준으로 산출된 값이라 FRED와는 애초에 안 맞는다. **유일한 유효 후보 = `ERPbymonth.xlsx`의 "$ Riskfree Rate"열**(카테고리18 내부, 짝인 ERP와 함께, 1001 발견)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>#15와 함께 재계산해 대조(단독 대조 무의미)</t>
+          <t>`ERPbymonth.xlsx` 최신행과 함께 재계산해 대조(FRED 단독 대조는 애초에 무의미)</t>
         </is>
       </c>
     </row>
@@ -5036,13 +5036,13 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="50.4" customWidth="1" min="2" max="2"/>
-    <col width="25.2" customWidth="1" min="3" max="3"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="44.1" customWidth="1" min="2" max="2"/>
+    <col width="19.8" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15.3" customWidth="1" min="7" max="7"/>
+    <col width="35.1" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -5091,27 +5091,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1(997)</t>
+          <t>**1(1001, 최우선 — 장은태 지시)**</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yahoo/Nasdaq 시총 대체경로</t>
+          <t>🔑 **Damodaran `ERPbymonth.xlsx` 월간 rf·ERP 페어 도입**</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#1 시가총액</t>
+          <t>**riskfree + ERP(짝)**</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>미해결14번(LOCAL_OK_PROD_FAIL) 우회 가능성</t>
+          <t>**7개월 정체 → 월 1회 갱신**</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + **의존관계#2**(자기자본·매출과 같은 주식수 기준이어야 함)</t>
+          <t>**조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리) 판정** — 짝 제약(의존관계#1)은 이미 충족됨(같은 파일·같은 행에서 rf·ERP를 함께 취득하므로), 남은 건 "어디에 코드를 붙이느냐"뿐. 날짜선택(§2-2)·폴백(§2-3)은 부차</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>있음(us_market_cap)</t>
+          <t>**카테고리 전환 5.9%(26/440) 실측**(1001 604전수)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>**예**</t>
         </is>
       </c>
     </row>
@@ -5138,22 +5138,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Damodaran `ratings.xls`(종목별 부채비용)</t>
+          <t>Yahoo/Nasdaq 시총 대체경로</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>#17 신용스프레드</t>
+          <t>#1 시가총액</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>업종평균 대신 종목별 이자보상배율 기반 부채비용</t>
+          <t>미해결14번(LOCAL_OK_PROD_FAIL) 우회 가능성</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>원전대조표</t>
+          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + **의존관계#2**(자기자본·매출과 같은 주식수 기준이어야 함)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>있음(WACC)</t>
+          <t>있음(us_market_cap)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Damodaran `fundgrEB.xls`(EBIT 성장률)</t>
+          <t>Damodaran `ratings.xls`(종목별 부채비용)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>역DCF 성장경로(층5, 범위 밖 슬롯)</t>
+          <t>#17 신용스프레드</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"가장 큰 구멍"의 비컨센서스 대안</t>
+          <t>업종평균 대신 종목별 이자보상배율 기반 부채비용</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>있음(GAP)</t>
+          <t>있음(WACC)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5222,37 +5222,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>~~Damodaran `histimpl.xls`(내재ERP)~~</t>
+          <t>Damodaran `fundgrEB.xls`(EBIT 성장률)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>#15 ERP</t>
+          <t>역DCF 성장경로(층5, 범위 밖 슬롯)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>🔴 **정정(1001) — histimpl.xls는 연간이라 부적합, 실제 후보는 `ERPbymonth.xlsx`(월간).** 아래 13번으로 대체됨, 이 행은 폐기</t>
+          <t>"가장 큰 구멍"의 비컨센서스 대안</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>원전대조표</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>있음(GAP)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>나스닥 Financial Status 플래그</t>
+          <t>~~Damodaran `histimpl.xls`(내재ERP)~~</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>상장상태/폐지위험(범위 밖 슬롯)</t>
+          <t>#15 ERP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상폐위험 조기신호</t>
+          <t>🔴 **정정(1001) — histimpl.xls는 연간이라 부적합, 실제 후보는 `ERPbymonth.xlsx`(월간).** 위 1번으로 대체됨, 이 행은 폐기</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>코드 없음, 데이터 이미 우리 유니버스 갱신 스크립트가 지나감</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>없음(신규 필드)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5306,64 +5306,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPDR 전 상품군(섹터ETF 외)</t>
+          <t>나스닥 Financial Status 플래그</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>#18 섹터분류</t>
+          <t>상장상태/폐지위험(범위 밖 슬롯)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>산업(서브섹터) 근사 가능성</t>
+          <t>상폐위험 조기신호</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>라이선스 문구 법무검토(997에서 이미 등재)</t>
+          <t>코드 없음, 데이터 이미 우리 유니버스 갱신 스크립트가 지나감</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>있음(섹터)</t>
+          <t>없음(신규 필드)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>필요(법무)</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7(998,R2)</t>
+          <t>7(997)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🔑 FRED ICE BofA OAS(등급별 매일 신용스프레드)</t>
+          <t>SPDR 전 상품군(섹터ETF 외)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#17 신용스프레드</t>
+          <t>#18 섹터분류</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Damodaran 연1회→매일 갱신으로 정밀도 개선 가능</t>
+          <t>산업(서브섹터) 근사 가능성</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>✅ **999 대조 완료 — 🟡 부분적 대응만 가능**(등급노치 손실·모집단차이·모델추정 vs 시장관측 개념차이). 직접 교체 불가, 하이브리드만 원리적으로 가능. **의존관계#5**(rf·ERP와 같은 as_of 배치)</t>
+          <t>라이선스 문구 법무검토(997에서 이미 등재)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>있음(WACC)</t>
+          <t>있음(섹터)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>필요(법무)</t>
         </is>
       </c>
     </row>
@@ -5390,37 +5390,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔑 FRED/Treasury 매일 국채수익률</t>
+          <t>🔑 FRED ICE BofA OAS(등급별 매일 신용스프레드)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>#14 무위험수익률</t>
+          <t>#17 신용스프레드</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Damodaran 연1회→매일</t>
+          <t>Damodaran 연1회→매일 갱신으로 정밀도 개선 가능</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🔴 **선택지A(rf만 교체) 철회(1001) — ERP와 짝 제약 있음(의존관계#1).** 999가 정의 일치·604전수 영향(1000: 6.4%)까지 확인했으나, **ERP를 같이 안 바꾸면 내적 모순**임을 849가 이미 기록해뒀던 것을 999·1000이 놓쳤다. → 13번(paired 안)으로 대체 검토 중</t>
+          <t>✅ **999 대조 완료 — 🟡 부분적 대응만 가능**(등급노치 손실·모집단차이·모델추정 vs 시장관측 개념차이). 직접 교체 불가, 하이브리드만 원리적으로 가능. **의존관계#5**(rf·ERP와 같은 as_of 배치)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>있음(WACC)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
@@ -5432,39 +5432,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Duke CFO Survey(분기 ERP)</t>
+          <t>~~FRED/Treasury 매일 국채수익률(raw)~~</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#15 ERP</t>
+          <t>#14 무위험수익률</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>서베이 기반 병기용(대체 아님)</t>
+          <t>🔴 **폐기(1002) — 후보 자격 자체가 없다.** 999의 "정의 완전일치" 판정이 오류였다: Damodaran이 실제 쓰는 rf는 raw Treasury가 아니라 별도의 "$ Riskfree Rate" 계열(1001 발견, 카테고리20 참조) — **짝 제약 문제 이전에 값 자체가 다른 계열**이라 raw FRED는 애초에 대체 후보가 못 된다. → 위 1번(`ERPbymonth.xlsx`의 "$ Riskfree Rate")으로 완전 대체</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>정의 차이(서베이 vs 시장내재) 화면 공개 필요</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>없음(병기 표시만)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>필요</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5474,37 +5470,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>edgartools(OSS, SEC 원문 그대로 재접근)</t>
+          <t>Duke CFO Survey(분기 ERP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>#4~#10 재무제표 전체</t>
+          <t>#15 ERP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>코드 대안(현재 route.ts 자체 파서 유지 이유 재확인용)</t>
+          <t>서베이 기반 병기용(대체 아님)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이득이 아니라 "현재 방식이 최선"이라는 대조 자료</t>
+          <t>정의 차이(서베이 vs 시장내재) 화면 공개 필요</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>없음(병기 표시만)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>불필요(정보용)</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
@@ -5516,27 +5512,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OpenFIGI(무료 식별자 매핑)</t>
+          <t>edgartools(OSS, SEC 원문 그대로 재접근)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#33(종목마스터, 슬롯 밖)</t>
+          <t>#4~#10 재무제표 전체</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CIK-티커 매핑 교차검증</t>
+          <t>코드 대안(현재 route.ts 자체 파서 유지 이유 재확인용)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CIK 필드 없음 — 티커 조인 검증 필요</t>
+          <t>이득이 아니라 "현재 방식이 최선"이라는 대조 자료</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5546,39 +5542,39 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요(정보용)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12(998,R3)</t>
+          <t>12(998,R2)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S&amp;P Global Market Intelligence가 동종서비스 대다수의 실제 소스</t>
+          <t>OpenFIGI(무료 식별자 매핑)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(참고, 슬롯 없음)</t>
+          <t>#33(종목마스터, 슬롯 밖)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>우리 "SEC원문+Damodaran" 조합이 여전히 드문 조합임을 재확인</t>
+          <t>CIK-티커 매핑 교차검증</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>판단 대상 아님(정보)</t>
+          <t>CIK 필드 없음 — 티커 조인 검증 필요</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5588,49 +5584,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>불필요</t>
+          <t>필요</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13(1001)</t>
+          <t>13(998,R3)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔑 **Damodaran `ERPbymonth.xlsx`(월간 rf·ERP 짝) — 8번의 대체안**</t>
+          <t>S&amp;P Global Market Intelligence가 동종서비스 대다수의 실제 소스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>#14 무위험수익률 + #15 ERP(짝으로 함께)</t>
+          <t>(참고, 슬롯 없음)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Damodaran 연1회(사실상 정체 7개월+)→월1회, **짝 유지**(의존관계#1 충족)</t>
+          <t>우리 "SEC원문+Damodaran" 조합이 여전히 드문 조합임을 재확인</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>✅ **1001 604전수 완료 — 전환 5.9%(26/440), 8번의 mismatched(6.4%)보다 낮음.** 방향은 가설과 일치하나 효과크기는 작음. 남은 선결: 조달 배치 위치(통합 vs 분리, 판정 안 함)·날짜선택(§2-2)·폴백(§2-3)</t>
+          <t>판단 대상 아님(정보)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>있음(WACC)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>불필요</t>
         </is>
       </c>
     </row>
@@ -9756,12 +9752,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21.6" customWidth="1" min="1" max="1"/>
-    <col width="30.6" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="57.6" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="59.4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -9817,81 +9813,99 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>내재 ERP 시계열(연도별, 월별 갱신 포함)</t>
+          <t>🔴 **정정(1002, 1001 발견 반영) — 연간뿐, "월별 갱신 포함"은 오류였다.** 내재 ERP 시계열(1960~, 연 1행 추가·연 1회 갱신). S&amp;P500 DDM/DCF 역산 내재 ERP — **역사적(realized) ERP가 아니라 시장 내재치**</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S&amp;P500 DDM/DCF 역산 내재 ERP — **역사적(realized) ERP가 아니라 시장 내재치**</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>🔑 **ERP 대안**(현재보다 자주 갱신되는 시장반영형)</t>
-        </is>
-      </c>
+          <t>~~ERP 대안(자주 갱신)~~ — **아래 `ERPbymonth.xlsx`가 진짜 월간 파일**(1001 발견, 998이 놓쳤던 별도 파일)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>`ctryprem.xlsx`(+연중 복수판)</t>
+          <t>🔑 **`ERPbymonth.xlsx`**(1001 발견, `/pc/implprem/ERPbymonth.xlsx`)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>국가별 디폴트스프레드·ERP·컨트리리스크프리미엄(150여개국)</t>
+          <t>rf·ERP **월간** 페어 시계열(2008-09~, 매월 1행) — `T.Bond Rate`(raw)와 `$ Riskfree Rate`(Damodaran 자체조정 계열, 산식 미공개) 두 rf가 같은 행에, ERP 5변형도 같은 행에</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>국가신용등급 기반</t>
+          <t>우리 저장값(rf=0.0395·erp=0.0446, as_of 2026-01)이 이 파일 2026-01행의 `$ Riskfree Rate`·`ERP(T12m)with adj riskfree rate`와 정확 일치 — **Damodaran이 실제로 쓰는 값의 원천이 이것**</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>🅿️ 파킹(비US 확장용, 지금 안 씀)</t>
+          <t>🔑 **#14/#15 즉시이득 최우선 후보**(아래 즉시이득표 1번 참조)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>`ratings.xls`</t>
+          <t>`ctryprem.xlsx`(+연중 복수판)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>신용등급대별 이자보상배율 구간·스프레드(대형/소형 별도표)</t>
+          <t>국가별 디폴트스프레드·ERP·컨트리리스크프리미엄(150여개국)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔑 다모다란 자신의 WACC 모델이 쓰는 "합성등급" 룩업테이블</t>
+          <t>국가신용등급 기반</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>🔑 **종목별 부채비용 산출 후보** — 현재 업종평균 WACC 대신 기업별 이자보상배율로 개별 신용스프레드 추정 가능</t>
+          <t>🅿️ 파킹(비US 확장용, 지금 안 씀)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>`ratings.xls`</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>신용등급대별 이자보상배율 구간·스프레드(대형/소형 별도표)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>🔑 다모다란 자신의 WACC 모델이 쓰는 "합성등급" 룩업테이블</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>🔑 **종목별 부채비용 산출 후보** — 현재 업종평균 WACC 대신 기업별 이자보상배율로 개별 신용스프레드 추정 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>`mktcaprisk.xlsx`</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>시총 구간별 베타·변동성</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>규모 10분위</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>미사용(대안 분류축)</t>
         </is>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>🔴 **정정(1002) — STEP999의 "완전 일치" 판정은 값 층위에서 오류였다.** 999는 정의 문구("10-year Treasury bond rate")만 대조해 일치를 확인했으나, **Damodaran이 실제로 ERP와 짝지어 쓰는 값은 raw Treasury가 아니라 별도의 자체조정 "$ Riskfree Rate" 계열**임을 1001이 발견했다(`ERPbymonth.xlsx` 직접 개봉, 산식 미공개). 우리 저장값 3.95%는 raw Treasury(FRED·`T.Bond Rate`≈4.18%)가 아니라 "$ Riskfree Rate"(0.0395)와 정확 일치 — **정의는 같은 말을 써도 실제 계열이 다르다.** 🔴 **결론: 카테고리20(raw Treasury, FRED 포함)은 #14 슬롯의 후보 부적격.** 유일한 유효 후보는 `ERPbymonth.xlsx`의 "$ Riskfree Rate"(카테고리18 내부, 짝인 ERP와 함께) — `docs/probe_999_fred_damodaran.json`(원 판정, 정정 대상)·`docs/probe_1001_erp_pair.json`(정정 근거)</t>
+          <t>🔴 **정정(1002) — STEP999의 "완전 일치" 판정은 값 층위에서 오류였다.** 999는 정의 문구("10-year Treasury bond rate")만 대조해 일치를 확인했으나, **Damodaran이 실제로 ERP와 짝지어 쓰는 값은 raw Treasury가 아니라 별도의 자체조정 "$ Riskfree Rate" 계열**임을 1001이 발견했다(`ERPbymonth.xlsx` 직접 개봉). 산식은 1003에서 확인됨 — `T.Bond rate − 해당등급 디폴트스프레드`(2025-05 Moody's 미국 신용등급 강등 대응, Damodaran 블로그 원문). 우리 저장값 3.95%는 raw Treasury(FRED·`T.Bond Rate`≈4.18%)가 아니라 "$ Riskfree Rate"(0.0395)와 정확 일치 — **정의는 같은 말을 써도 실제 계열이 다르다.** 🔴 **결론: 카테고리20(raw Treasury, FRED 포함)은 #14 슬롯의 후보 부적격.** 유일한 유효 후보는 `ERPbymonth.xlsx`의 "$ Riskfree Rate"(카테고리18 내부, 짝인 ERP와 함께) — `docs/probe_999_fred_damodaran.json`(원 판정, 정정 대상)·`docs/probe_1001_erp_pair.json`(정정 근거)</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35.1" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>**조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리) 판정** — 짝 제약(의존관계#1)은 이미 충족됨(같은 파일·같은 행에서 rf·ERP를 함께 취득하므로), 남은 건 "어디에 코드를 붙이느냐"뿐. 날짜선택(§2-2)·폴백(§2-3)은 부차</t>
+          <t>🟢 **상태(1003): 구현 완료·적재 대기.** `lib/revdcf/erpMonthly.ts`(순수함수, 값불변증명 통과) 구현·클린클론빌드 통과. 남은 선결 — 조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리, 미결) · 스키마 설계(같은 행 `expected_inflation` 공존 문제 + `damodaran_global_inputs`가 현재 정확히 1행이고 `.single()`로 읽혀 새 as_of를 naive 삽입하면 크론이 깨지는 위험 — 1003이 발견, 컬럼추가안 vs 별도테이블안 미결) · 날짜선택(§2-2)·폴백(§2-3)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>**카테고리 전환 5.9%(26/440) 실측**(1001 604전수)</t>
+          <t>**카테고리 전환 5.9%(26/440) 재확인**(1003, 오늘 기준 최신월도 동일값)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7097,7 +7097,7 @@
     <col width="51.3" customWidth="1" min="2" max="2"/>
     <col width="46.8" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="48.6" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7589,17 +7589,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>999-1001</t>
+          <t>999-1003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>무위험수익률 소스 — FRED만 교체 → 짝 필요 발견 → ERPbymonth.xlsx 페어 권고</t>
+          <t>무위험수익률 소스 — FRED만 교체 → 짝 필요 발견 → ERPbymonth.xlsx 페어 구현</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>선택지A 철회 → 선택지C 권고(판정 대기)</t>
+          <t>선택지A 철회 → 선택지C 구현완료(적재 대기)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Damodaran의 "$ Riskfree Rate" 산식 미규명 — 확인 필요</t>
+          <t>Damodaran의 "$ Riskfree Rate" 산식 — 1003에서 확인됨(2025-05 Moody's 미국 신용등급 강등 대응, T.Bond rate−디폴트스프레드)</t>
         </is>
       </c>
     </row>
@@ -9831,17 +9831,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rf·ERP **월간** 페어 시계열(2008-09~, 매월 1행) — `T.Bond Rate`(raw)와 `$ Riskfree Rate`(Damodaran 자체조정 계열, 산식 미공개) 두 rf가 같은 행에, ERP 5변형도 같은 행에</t>
+          <t>rf·ERP **월간** 페어 시계열(2008-09~, 매월 1행) — `T.Bond Rate`(raw)와 `$ Riskfree Rate`(Damodaran 자체조정 계열) 두 rf가 같은 행에, ERP 5변형도 같은 행에. 🔴 **정정(1003) — 산식은 공개돼 있다.** `$ Riskfree Rate = T.Bond rate − 해당등급 디폴트스프레드`(Moody's 2025-05-16 미국 Aaa→Aa1 강등에 대한 Damodaran의 대응, "Sovereign Ratings, Default Risk and Markets" 2025-06 블로그 원문 확인)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>우리 저장값(rf=0.0395·erp=0.0446, as_of 2026-01)이 이 파일 2026-01행의 `$ Riskfree Rate`·`ERP(T12m)with adj riskfree rate`와 정확 일치 — **Damodaran이 실제로 쓰는 값의 원천이 이것**</t>
+          <t>우리 저장값(rf=0.0395·erp=0.0446, as_of 2026-01)이 이 파일 2026-01행의 `$ Riskfree Rate`·`ERP(T12m)with adj riskfree rate`와 정확 일치 — **Damodaran이 실제로 쓰는 값의 원천이 이것**. 단 Damodaran 자신의 요약시트는 raw T.Bond Rate+plain ERP(T12m) 조합을 더 눈에 띄게 제시(1003 발견, 다른 조합)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>🔑 **#14/#15 즉시이득 최우선 후보**(아래 즉시이득표 1번 참조)</t>
+          <t>🔑 **#14/#15 즉시이득 최우선 후보 — 1003에서 구현 완료(미배선)**(아래 즉시이득표 1번 참조)</t>
         </is>
       </c>
     </row>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟢 **상태(1003): 구현 완료·적재 대기.** `lib/revdcf/erpMonthly.ts`(순수함수, 값불변증명 통과) 구현·클린클론빌드 통과. 남은 선결 — 조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리, 미결) · 스키마 설계(같은 행 `expected_inflation` 공존 문제 + `damodaran_global_inputs`가 현재 정확히 1행이고 `.single()`로 읽혀 새 as_of를 naive 삽입하면 크론이 깨지는 위험 — 1003이 발견, 컬럼추가안 vs 별도테이블안 미결) · 날짜선택(§2-2)·폴백(§2-3)</t>
+          <t>🟢 **상태(1004): `.single()` 파손 위험 해소·구현 완료·적재 대기.** `lib/revdcf/erpMonthly.ts`(순수함수, 값불변증명 통과) 구현. 🟢 **1003이 발견한 파손 위험(`damodaran_global_inputs`가 정확히 1행이라 `.single()`로 읽혔음 — 새 as_of 삽입 시 크론이 죽는 문제)은 1004에서 해소됨**(damodaran_* 12개 읽기 지점 전부 최신 as_of 조회로 전환, 604전수 값불변 확인, 클린클론빌드 통과) — 이제 적재해도 크론이 안 죽는다. 남은 선결 — 조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리, 미결) · 스키마 설계(같은 행 `expected_inflation` 공존 문제, 컬럼추가안 vs 별도테이블안 미결) · 날짜선택(§2-2)·폴백(§2-3)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -5042,8 +5042,8 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="45.9" customWidth="1" min="7" max="7"/>
+    <col width="13.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟢 **상태(1004): `.single()` 파손 위험 해소·구현 완료·적재 대기.** `lib/revdcf/erpMonthly.ts`(순수함수, 값불변증명 통과) 구현. 🟢 **1003이 발견한 파손 위험(`damodaran_global_inputs`가 정확히 1행이라 `.single()`로 읽혔음 — 새 as_of 삽입 시 크론이 죽는 문제)은 1004에서 해소됨**(damodaran_* 12개 읽기 지점 전부 최신 as_of 조회로 전환, 604전수 값불변 확인, 클린클론빌드 통과) — 이제 적재해도 크론이 안 죽는다. 남은 선결 — 조달 배치 위치(`ingest_damodaran.ts` 통합 vs 분리, 미결) · 스키마 설계(같은 행 `expected_inflation` 공존 문제, 컬럼추가안 vs 별도테이블안 미결) · 날짜선택(§2-2)·폴백(§2-3)</t>
+          <t>🟢 **상태(1005): 적재 완료·크론 반영 대기.** `scripts/ingest_erp_monthly.ts`로 `damodaran_global_inputs`에 새 행(as_of=2026-08-01) INSERT 완료 — 기존 행 지문 불변 확인, 새 행 rf·erp 정확 일치. **헤드라인 검증 — 실제 프로덕션 2행 상태에서 `latestAsOf()`가 새 행을 정확히 고름을 확인**(1004 수정의 첫 실전 검증). rf·erp는 ERPbymonth(2026-08) 유래, `global_default_spread`·`marginal_tax_rate_used`·`expected_inflation`은 wacc.xls(2026-01-05) 그대로 복사(한 행 안에서 출처 혼재, 기록방식은 문서화만 — 옵션A 컬럼추가는 보류·재고권고). 다음 정규크론이 `revdcf_results` 26건 verdict 변경 반영 예정(단 `revdcfEnabled()` 기본OFF라 화면 노출은 별개 승인)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>**카테고리 전환 5.9%(26/440) 재확인**(1003, 오늘 기준 최신월도 동일값)</t>
+          <t>**카테고리 전환 5.9%(26/440) 재확인**(1005, 라이브 로드값 그대로 재계산)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>**예**</t>
+          <t>**예(배포 승인 대기)**</t>
         </is>
       </c>
     </row>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3927,7 +3927,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yahoo 배치조회(정본, us_market_cap)</t>
+          <t>~~Yahoo 배치조회(정본, us_market_cap)~~ → Yahoo 3단 취득(배치→개별재시도 400건/40s→7일폴백)(정본, us_market_cap. lib/lensPrecompute.ts:107-236) (1011 정정 — 코드 대조 결과 배치 1단계만 기재돼 있었음, 실제론 개별재시도·7일폴백 2단계가 더 있다)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEC XBRL 태그(역DCF), Yahoo 부수값(밸류)</t>
+          <t>SEC XBRL 태그(역DCF), ~~Yahoo 부수값(밸류)~~ → (밸류에이션은 shares 미사용 — marketCap 직접사용, lib/valuation.ts:38-49 ValuationInputs에 shares 필드 자체가 없음) (1011 정정 — 코드 근거 없는 서술이었음. 부수 발견: us_fundamentals.source_tags에 shares 키 없음, 채택 태그명은 revdcf_results.flags.sharesTag에만 실림·604건 한정)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Damodaran wacc.xls 상단값(연1회라 서술되나 실질 정체 7개월+)</t>
+          <t>~~Damodaran wacc.xls 상단값(연1회라 서술되나 실질 정체 7개월+)~~ → Damodaran ERPbymonth.xlsx "$ Riskfree Rate"열(월1회, STEP1005가 새 행 as_of=2026-08-01 적재 — damodaran_global_inputs가 이제 2행이고 latestAsOf()가 항상 최신행을 골라 이 값이 프로덕션에서 실제로 쓰이는 중. wacc.xls 유래 구행[as_of=2026-01-05]은 테이블에 남아있으나 더 이상 안 읽힘) (1011 정정 — 카탈로그가 아직 옛 소스로 적혀 있던 것을 STEP1011이 최초로 코드 대조로 발견)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Damodaran wacc.xls 상단값(연1회, 사실상 정체 7개월+)</t>
+          <t>~~Damodaran wacc.xls 상단값(연1회, 사실상 정체 7개월+)~~ → Damodaran ERPbymonth.xlsx "ERP(T12m) with adj riskfree rate"열(#14와 같은 행에서 짝으로 옴, as_of=2026-08-01 활성) (1011 정정 — #14와 동일 사유)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>resolveSector() 0~4순위(SPDR→Damodaran→형제→야후→미분류)</t>
+          <t>resolveSector() 0~4순위(SPDR→Damodaran→형제→야후→미분류) — 추가: us_sector_wide는 새 as_of를 안 만들고 기존 as_of(현재 2026-08-08)에 신규 심볼만 append(STEP974 방식ⓐ, route.ts:116-148) (1011 정정 — 알고리즘명은 정확했으나 갱신방식이 누락돼 있었음)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5460,7 +5460,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9821,7 +9820,6 @@
           <t>~~ERP 대안(자주 갱신)~~ — **아래 `ERPbymonth.xlsx`가 진짜 월간 파일**(1001 발견, 998이 놓쳤던 별도 파일)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -5153,7 +5153,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + **의존관계#2**(자기자본·매출과 같은 주식수 기준이어야 함)</t>
+          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + 의존관계#2(자기자본·매출과 같은 주식수 기준이어야 함) | STEP1012 실측(2026-08-13): quoteSummary(후보2)는 STEP1010이 0/284로 사망 처리. Nasdaq(후보1) 환경차이 커버리지 73.2%(208/284), 배선시 예상 (5601+208)/5973=97.25%로 게이트 통과 가능. 단 겹치는 208건 중 13.5~20.2%가 야후값과 20%초과 차이(보정전/후), $0.3B~2B구간 22~31%로 소형중형주 정의불일치 위험 큼. 재수집 스크립트(ingest_us_sector.ts)는 존재하나 로컬 스냅샷만 읽음(라이브fetch로 바꿔야 매일갱신). 상세=docs/probe_1012_nasdaq_marketcap.md</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -5153,7 +5153,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + 의존관계#2(자기자본·매출과 같은 주식수 기준이어야 함) | STEP1012 실측(2026-08-13): quoteSummary(후보2)는 STEP1010이 0/284로 사망 처리. Nasdaq(후보1) 환경차이 커버리지 73.2%(208/284), 배선시 예상 (5601+208)/5973=97.25%로 게이트 통과 가능. 단 겹치는 208건 중 13.5~20.2%가 야후값과 20%초과 차이(보정전/후), $0.3B~2B구간 22~31%로 소형중형주 정의불일치 위험 큼. 재수집 스크립트(ingest_us_sector.ts)는 존재하나 로컬 스냅샷만 읽음(라이브fetch로 바꿔야 매일갱신). 상세=docs/probe_1012_nasdaq_marketcap.md</t>
+          <t>계산기준 검증(카테고리1·2·3 구분) 먼저 + 의존관계#2(자기자본·매출과 같은 주식수 기준이어야 함) | STEP1012 실측(2026-08-13): quoteSummary(후보2)는 STEP1010이 0/284로 사망 처리. Nasdaq(후보1) 환경차이 커버리지 73.2%(208/284), 배선시 예상 (5601+208)/5973=97.25%로 게이트 통과 가능. 단 겹치는 208건 중 13.5~20.2%가 야후값과 20%초과 차이(보정전/후), $0.3B~2B구간 22~31%로 소형중형주 정의불일치 위험 큼. 재수집 스크립트(ingest_us_sector.ts)는 존재하나 로컬 스냅샷만 읽음(라이브fetch로 바꿔야 매일갱신). 상세=docs/probe_1012_nasdaq_marketcap.md | STEP1013(2026-08-13) 매일갱신 배선됨: lib/nasdaqMarketCap.ts(라이브취득) + us_market_cap_nasdaq(신규테이블, us_market_cap과 완전별도) + app/api/cron/us-perf/route.ts(22:00 UTC 부속, try/catch 완전격리). 이 STEP은 재수집만 — us_market_cap·게이트에는 아직 안섞임(폴백배선은 장은태판정 이후). D-1지연 주의(lens-scores 21:30 UTC가 먼저 돎). 상세=docs/probe_1013_nasdaq_ingest.md</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(우리 정본, SEC 주식수×종가로 직접 조립)</t>
+          <t>~~(우리 정본, SEC 주식수×종가로 직접 조립)~~ → 실측 완료(1019): 단독커버리지76.2%·결측코호트결합96.95%, 97%게이트 미달 — 정본 아님</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>975 정본 — 외부 대조 시 이 기준</t>
+          <t>~~975 정본 — 외부 대조 시 이 기준~~ → 참고 계열로만 유효(1019 정정), 어떤 계산에도 미사용</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>섹터·🔑 **시총 대체경로 후보**(§3-3)</t>
+          <t>섹터·🔑 시총대체경로 후보 → 🔴 정정(1017/1018/1019): 접근불가 확정(20초·60초 timeout 전부실패·robots.txt disallow), 후보소진</t>
         </is>
       </c>
     </row>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_2" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_3" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_4" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유니버스 종류 구성 (1021 신규)" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8305,6 +8306,221 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>종류</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>판별 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COMMON(잔여)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5124</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>패턴 불일치 → 보통주 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CEF_TRUST(펀드·신탁 명칭)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>320</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>이름패턴 추정 — 7건 REIT오분류 확인(FRT·EQR·CPT·AMH·NTRS·ESS·DLR), 나머지 313건은 lens_scores/revdcf 어디에도 없어 진짜 CEF 가능성 높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>306</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>American Depositary Shares/ADS/ADR(철자변형 Depository 미포착)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>217</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Acquisition Corp + Ordinary/Class 주식</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>로열티트러스트</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Royalty Trust/Units of Beneficial Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>우선주·워런트·라이트</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>refresh_us_symbols.ts EXCLUDE_NAME 정규식이 이미 걸러냄(정상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>핵심 발견</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>revdcf_results(604건)엔 CEF·신탁·SPAC 0건 — 모델이 이미 정상 배제 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>가상 커버리지(채택 안 함)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEF/신탁 제외 시 96.95%→98.39%(97%게이트 넘김) — 판정은 장은태 몫</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>docs/probe_1021_universe_composition.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3960,7 +3960,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEC XBRL 태그(역DCF), ~~Yahoo 부수값(밸류)~~ → (밸류에이션은 shares 미사용 — marketCap 직접사용, lib/valuation.ts:38-49 ValuationInputs에 shares 필드 자체가 없음) (1011 정정 — 코드 근거 없는 서술이었음. 부수 발견: us_fundamentals.source_tags에 shares 키 없음, 채택 태그명은 revdcf_results.flags.sharesTag에만 실림·604건 한정)</t>
+          <t>SEC XBRL 태그(역DCF), ~~Yahoo 부수값(밸류)~~ → (밸류에이션은 shares 미사용 — marketCap 직접사용, lib/valuation.ts:38-49 ValuationInputs에 shares 필드 자체가 없음) (1011 정정 — 코드 근거 없는 서술이었음. 부수 발견: us_fundamentals.source_tags에 shares 키 없음, 채택 태그명은 revdcf_results.flags.sharesTag에만 실림·604건 한정) 🔴 STEP1022 추가 — SEC frames 조회창 결함: 이 세션 조사스크립트의 6분기 조회창(probe_1019_sec_marketcap_assembly.ts:74)은 근거없는 임의값(조사스크립트 한정, 프로덕션 아님). companyfacts는 창 없이 전체이력 반환 — 182건 전수재조회 결과 회복 18건(9.9%)뿐 그중17건 시점중앙값5.3년 낡음(무용지물 수준). 더 중요: 기존충족 4,557건 전수재조회 결과 322건(7.07%)이 프레임보다 더 최신값 보유(중앙값49일·p90 86일). 상세=docs/probe_1022_sec_window_audit.md</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -41,6 +41,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_3" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_4" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유니버스 종류 구성 (1021 신규)" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-A 분자 경로 소진 (1023 신규)" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3960,7 +3961,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SEC XBRL 태그(역DCF), ~~Yahoo 부수값(밸류)~~ → (밸류에이션은 shares 미사용 — marketCap 직접사용, lib/valuation.ts:38-49 ValuationInputs에 shares 필드 자체가 없음) (1011 정정 — 코드 근거 없는 서술이었음. 부수 발견: us_fundamentals.source_tags에 shares 키 없음, 채택 태그명은 revdcf_results.flags.sharesTag에만 실림·604건 한정) 🔴 STEP1022 추가 — SEC frames 조회창 결함: 이 세션 조사스크립트의 6분기 조회창(probe_1019_sec_marketcap_assembly.ts:74)은 근거없는 임의값(조사스크립트 한정, 프로덕션 아님). companyfacts는 창 없이 전체이력 반환 — 182건 전수재조회 결과 회복 18건(9.9%)뿐 그중17건 시점중앙값5.3년 낡음(무용지물 수준). 더 중요: 기존충족 4,557건 전수재조회 결과 322건(7.07%)이 프레임보다 더 최신값 보유(중앙값49일·p90 86일). 상세=docs/probe_1022_sec_window_audit.md</t>
+          <t>SEC XBRL 태그(역DCF), ~~Yahoo 부수값(밸류)~~ → (밸류에이션은 shares 미사용 — marketCap 직접사용, lib/valuation.ts:38-49 ValuationInputs에 shares 필드 자체가 없음) (1011 정정 — 코드 근거 없는 서술이었음. 부수 발견: us_fundamentals.source_tags에 shares 키 없음, 채택 태그명은 revdcf_results.flags.sharesTag에만 실림·604건 한정) 🔴 STEP1022 추가 — SEC frames 조회창 결함: 이 세션 조사스크립트의 6분기 조회창(probe_1019_sec_marketcap_assembly.ts:74)은 근거없는 임의값(조사스크립트 한정, 프로덕션 아님). companyfacts는 창 없이 전체이력 반환 — 182건 전수재조회 결과 회복 18건(9.9%)뿐 그중17건 시점중앙값5.3년 낡음(무용지물 수준). 더 중요: 기존충족 4,557건 전수재조회 결과 322건(7.07%)이 프레임보다 더 최신값 보유(중앙값49일·p90 86일). 상세=docs/probe_1022_sec_window_audit.md 🔴 STEP1023 정정 — 위 "322건"은 프로덕션 데이터가 아니다. probe_1022_sec_window_audit.ts에 us_fundamentals 참조 0건(직접 확인) — 322건은 이 조사 스크립트가 자체적으로 만든 두 임시값(구기준선=frames 6분기창 / 신기준선=companyfacts 전체이력) 사이의 비교였고 어느 쪽도 DB에 저장된 적이 없다. 프로덕션(app/api/cron/revdcf/route.ts:278-281)은 애초에 frames를 쓴 적이 없다 — companyfacts(창 없는 전체이력)를 직접 호출하고, 태그 우선순위도 다르며(WeightedAverageNumberOfDilutedSharesOutstanding 최우선, lib/revdcf/drivers.ts:365-373), 복수클래스는 이미 MULTI_CLASS_SHARES로 스킵 처리된다(drivers.ts:375-384). 7.07%는 조사 도구 내부 현상이었지 us_fundamentals.shares의 실제 낡음률이 아니다. 상세=docs/probe_1023_stale_shares_impact.md</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8521,6 +8522,179 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>경로</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>야후 quote(현재 정본)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>93.9%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16일째 게이트 미달</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>야후 quoteSummary</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0/284</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>STEP1010 — 프로파일 필드가 프로덕션 환경 자체에서 전부 결측(직렬화 문제 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>나스닥 스크리너</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>접근 불가</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>robots.txt disallow · 60초로 늘려도 timeout(STEP1017·1018·1019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SEC 자체 조립(주식수×종가)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>96.95%(엄격 95.96%)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>97% 게이트에 근소 미달(STEP1019·1020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SEC 조회창 확장(frames→companyfacts)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+18건(9.9%)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>그중 17건은 중앙값 5.3년(최대 16.6년) 낡아 실질 +1건(STEP1022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>결론</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>다섯 경로 전부 막히거나 소진. 남은 경로 = 분모(유니버스 재정의)뿐이나 분류 정확도 검증이 선결(CEF/신탁 320건 중 7건 REIT 오분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>부수 확인</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>조회창 확장이 찾은 322건 낡음은 커버리지가 아니라 이미 채워진 값의 정확도 문제였으나, STEP1023이 이 322건 자체가 조사 스크립트 내부 비교였을 뿐 프로덕션(us_fundamentals.shares)과 무관함을 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>docs/probe_1023_stale_shares_impact.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과거 판정 흡수 (신규, 1002)_4" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유니버스 종류 구성 (1021 신규)" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-A 분자 경로 소진 (1023 신규)" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유니버스 SIC 정본 (1024 신규)" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8528,7 +8529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8653,7 +8654,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -8687,6 +8687,269 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>docs/probe_1023_stale_shares_impact.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STEP1024 추가</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>분모(유니버스) 경로도 소진 — SIC로 정확히 골라 SPAC 272건만 제외해도 96.95%-&gt;96.91%로 하락. 분자+분모 둘 다 소진, 남은 것은 게이트 임계 재검토(장은태 판정)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SIC 종류</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COMMON_SIC(사업 SIC 보유)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5134</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>85.91%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>최소 11건이 SIC 0000(미분류 플레이스홀더) 오염 — 전체 규모 미측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>REIT_6798</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>178</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>제외 대상 아님. 정상 운영회사</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CEF_FUND_6726</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>등록 CEF는 1940년법 투자회사라 SIC 자체가 없음(entityType=other) — 정본 미실사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SPAC_6770(Blank Checks)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>272</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1021 이름패턴(217건)보다 55건 많음. 15건은 6770 아닌 사업코드로 채워짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>판별불가_투자회사(entityType!=operating, SIC없음)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>321</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.37%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>진짜 CEF 신호(CEF_TRUST 명칭 236건과 일치) — 외국상장사도 같은 신호라 단독 판별력 약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>판별불가_SIC없음</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>판별불가_CIK없음</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1021과의 핵심 차이</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7건-&gt;54건(REIT 오분류 전수), NTRS는 REIT 아닌 은행(SIC 6022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>가상 커버리지(채택 안 함)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SIC 6726(0)+6770(272) 제외 시 96.95%-&gt;96.91%(하락, 1021의 98.39%는 산술착시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>교차검증</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>lens_scores(1036)/revdcf_results(604) 내 SIC 제외후보=0건. entityType!=operating 190건도 전부 외국상장사, CEF 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>docs/probe_1024_universe_sic.md</t>
         </is>
       </c>
     </row>

--- a/docs/data_source_catalog.xlsx
+++ b/docs/data_source_catalog.xlsx
@@ -3930,7 +3930,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>~~Yahoo 배치조회(정본, us_market_cap)~~ → Yahoo 3단 취득(배치→개별재시도 400건/40s→7일폴백)(정본, us_market_cap. lib/lensPrecompute.ts:107-236) (1011 정정 — 코드 대조 결과 배치 1단계만 기재돼 있었음, 실제론 개별재시도·7일폴백 2단계가 더 있다)</t>
+          <t>~~Yahoo 배치조회(정본, us_market_cap)~~ → Yahoo 3단 취득(배치→개별재시도 400건/40s→7일폴백)(정본, us_market_cap. lib/lensPrecompute.ts:107-236 — 🔴 정정(STEP1034, 2026-08-15): 현재는 lib/lensPrecompute.ts:146-300(1025·1031·1032가 파일 앞부분에 코드를 추가해 39줄 밀림, 알고리즘 자체는 무변경. 배치:161-180·개별재시도:181-221·7일폴백:222-299)) (1011 정정 — 코드 대조 결과 배치 1단계만 기재돼 있었음, 실제론 개별재시도·7일폴백 2단계가 더 있다)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🟡 부분 — 1002가 #19(오류 발견·정정)·#20(중복 발견·병합)을 검증. 나머지 슬롯은 대체로 이전 STEP들에서 이미 코드로 확인됐으나 **전 슬롯 일괄 재검증은 이번에도 안 함**(못 한 것 참조)</t>
+          <t>✅ 완료(STEP1011·STEP1034) — 🔴 정정(STEP1034): 이 행이 1002 기준으로 멈춰 있었으나, STEP1011(2026-08-13)이 이미 20개 전부 일괄 코드 대조를 완료했다(일치15/불일치5). STEP1034(2026-08-15)가 그 이후 변경분(git log로 전수 확인, 1건만 해당)까지 재대조해 지금도 유효함을 확인</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8553,6 +8553,11 @@
           <t>근거</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>🔴 85% 기준(STEP1034 정정)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -8573,6 +8578,11 @@
           <t>16일째 게이트 미달</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>통과(94.16%, 08-14 실측)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -8593,6 +8603,11 @@
           <t>STEP1010 — 프로파일 필드가 프로덕션 환경 자체에서 전부 결측(직렬화 문제 아님)</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>해당없음(경로 자체 죽음, 게이트 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8613,6 +8628,11 @@
           <t>robots.txt disallow · 60초로 늘려도 timeout(STEP1017·1018·1019)</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>해당없음(게이트와 무관한 별개 장벽 — robots.txt 차단)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8633,6 +8653,11 @@
           <t>97% 게이트에 근소 미달(STEP1019·1020)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>통과(96.95%, 야후 94.16%보다 높음 — 재검토 목록)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8653,6 +8678,11 @@
           <t>그중 17건은 중앙값 5.3년(최대 16.6년) 낡아 실질 +1건(STEP1022)</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>개선폭 작아 통과 여부 무영향</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8690,7 +8720,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -8700,6 +8729,18 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>분모(유니버스) 경로도 소진 — SIC로 정확히 골라 SPAC 272건만 제외해도 96.95%-&gt;96.91%로 하락. 분자+분모 둘 다 소진, 남은 것은 게이트 임계 재검토(장은태 판정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STEP1034 정정(2026-08-15)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>이 시트 전체가 고정 97% 게이트 기준 판정이었다. STEP1031(2026-08-14)이 게이트를 절대하한 85%+낙폭상한 3%p로 실전환하면서 경로 1·4·5(야후·SEC자체조립·유니버스정리후)가 85% 기준으로는 통과. "분자/분모 경로 소진"·"게이트 임계 재검토는 장은태 판정"(A12 행)이라는 결론은 더 이상 유효하지 않다 — 그 재검토 자체가 STEP1031에서 이미 실행됐다. 단 SEC 자체조립을 정본으로 쓸지는 이 STEP도 판정하지 않음(재검토 목록, docs/probe_1034_catalog_sync.md)</t>
         </is>
       </c>
     </row>
